--- a/app_lealtad/CheckListAppLealtad.xlsx
+++ b/app_lealtad/CheckListAppLealtad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/proyecto/app_lealtad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CCD5E9-C00A-274F-B9DC-0562FE64B4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D44AB83-5133-484F-852D-BB697E93F166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,11 +25,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+  <si>
+    <t>System Status</t>
+  </si>
   <si>
     <t>CPU Utilization Last Hour</t>
   </si>
   <si>
+    <t>Network In Last Hour</t>
+  </si>
+  <si>
+    <t>Network Out Last Hour</t>
+  </si>
+  <si>
+    <t>Volumen EBS</t>
+  </si>
+  <si>
+    <t>Volumen  Status</t>
+  </si>
+  <si>
+    <t>Read Ops</t>
+  </si>
+  <si>
+    <t>Write Ops</t>
+  </si>
+  <si>
     <t>Min</t>
   </si>
   <si>
@@ -51,47 +72,49 @@
     <t>Date Last Snapshot</t>
   </si>
   <si>
+    <t>RDS CLOUDWATCH</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
     <t>Notas</t>
   </si>
   <si>
+    <t>Instancias</t>
+  </si>
+  <si>
+    <t>Instance Status</t>
+  </si>
+  <si>
+    <t>Nombre de la Instancia</t>
+  </si>
+  <si>
     <t>Id de la Instancia</t>
   </si>
   <si>
     <t>Disponibilidad de la URL / Página web</t>
   </si>
   <si>
-    <t>Nombre de la función</t>
-  </si>
-  <si>
-    <t>Duración Promedio</t>
-  </si>
-  <si>
-    <t>Total de errores</t>
-  </si>
-  <si>
-    <t>Total de invocaciones</t>
-  </si>
-  <si>
-    <t>Lambdas</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>LOGS EN "darrow-database-web"</t>
+    <t>Free Storages Space Last Hour</t>
   </si>
   <si>
     <t>La revisión realizada se basa en los siguientes criterios:
-* CPU Utilization: Confirmación de que el uso de CPU se mantenga por debajo del 85%.
+* Status Check: Verificación del estado de la instancia, asegurando que el sistema y el volumen se encuentren en "OK".
+* CPU Utilization: Confirmación de que el uso de CPU se mantenga por debajo del 85%, tanto en las instancias como en la RDS.
 * Snapshot: Validación de la creación del respaldo correspondiente al día anterior en la RDS.
+* Free Storage Space: Verificación de que el espacio libre en la RDS sea superior a 10 GB.
 Recomendación: No depender únicamente de los comentarios anexados; se sugiere realizar una revisión adicional para mayor precisión.</t>
+  </si>
+  <si>
+    <t>ERROR EN LOS LOGS EN "database-1ceca-resp-instance-1-reader"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -118,11 +141,33 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow (Cuerpo)"/>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="14"/>
       <color theme="0"/>
@@ -130,17 +175,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="15"/>
-      <color theme="1"/>
+      <sz val="14"/>
+      <color theme="0"/>
       <name val="Aptos Narrow (Cuerpo)"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,6 +191,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF8ED873"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -168,6 +214,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFA9C"/>
+        <bgColor rgb="FF93C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor rgb="FF8ED873"/>
       </patternFill>
     </fill>
@@ -177,14 +235,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="30">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -213,6 +265,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -352,6 +413,15 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -447,79 +517,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -535,83 +533,124 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -619,35 +658,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -655,30 +667,33 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,476 +918,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:V1001"/>
+  <dimension ref="B1:U1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="39.5" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="14" width="10.5" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" customWidth="1"/>
-    <col min="16" max="16" width="49.6640625" customWidth="1"/>
-    <col min="17" max="19" width="15.6640625" customWidth="1"/>
-    <col min="20" max="27" width="10.5" customWidth="1"/>
+    <col min="5" max="13" width="10.5" customWidth="1"/>
+    <col min="14" max="14" width="27.1640625" customWidth="1"/>
+    <col min="15" max="15" width="10.5" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15.75" customHeight="1"/>
-    <row r="2" spans="2:22" ht="27" customHeight="1">
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:21" ht="27" customHeight="1">
+      <c r="B2" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="30"/>
+    </row>
+    <row r="3" spans="2:21" ht="27" customHeight="1">
+      <c r="B3" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="49"/>
-      <c r="P2" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-    </row>
-    <row r="3" spans="2:22" ht="27" customHeight="1">
-      <c r="B3" s="50" t="s">
+      <c r="O3" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" s="23"/>
+      <c r="U3" s="24"/>
+    </row>
+    <row r="4" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="41"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="43"/>
-      <c r="P3" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q3" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="R3" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" s="36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" ht="22" customHeight="1">
-      <c r="B4" s="51"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="46"/>
-      <c r="N4" s="44"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B5" s="52"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="6"/>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="2:22" ht="15.75" customHeight="1">
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="2:22" ht="16" customHeight="1">
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="4"/>
-    </row>
-    <row r="8" spans="2:22" ht="22" customHeight="1">
-      <c r="B8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="H8" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="35"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-    </row>
-    <row r="10" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="2:22" ht="14" customHeight="1">
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="2:22" ht="13" customHeight="1">
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="2:22" ht="15.75" customHeight="1">
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="2:22" ht="15.75" customHeight="1">
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="2:22" ht="15.75" customHeight="1">
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="2:22" ht="23" customHeight="1">
-      <c r="B16" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="V16" s="5"/>
-    </row>
-    <row r="17" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="V17" s="5"/>
-    </row>
-    <row r="18" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="2:22" ht="17" customHeight="1">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="2:22" ht="14" customHeight="1">
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="2:22" ht="15.75" customHeight="1">
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="2:22" ht="24" customHeight="1">
-      <c r="B22" s="22" t="s">
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="2:21" ht="15.75" customHeight="1"/>
+    <row r="11" spans="2:21" ht="15.75" customHeight="1"/>
+    <row r="12" spans="2:21" ht="27" customHeight="1">
+      <c r="B12" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" spans="2:21" ht="18" customHeight="1">
+      <c r="B13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="58"/>
+      <c r="O13" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="50"/>
+    </row>
+    <row r="14" spans="2:21" ht="19.5" customHeight="1">
+      <c r="B14" s="16"/>
+      <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="2:22" ht="15" customHeight="1">
-      <c r="B23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="2:22" ht="15" customHeight="1">
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="2:22" ht="17" customHeight="1">
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="2:22" ht="15" customHeight="1">
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="2:22" ht="15" customHeight="1">
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="18"/>
-    </row>
-    <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="37" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="38" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="39" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="40" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="41" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="42" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="43" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="44" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="45" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="46" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="47" spans="2:7" ht="15.75" customHeight="1"/>
-    <row r="48" spans="2:7" ht="15.75" customHeight="1"/>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="59"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="27"/>
+    </row>
+    <row r="15" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="20"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="43"/>
+    </row>
+    <row r="16" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B16" s="2"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="43"/>
+    </row>
+    <row r="17" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O17" s="12"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+    </row>
+    <row r="18" spans="2:21" ht="27" customHeight="1">
+      <c r="B18" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="H18" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="53"/>
+    </row>
+    <row r="19" spans="2:21" ht="19" customHeight="1">
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="56"/>
+    </row>
+    <row r="21" spans="2:21" ht="15.75" customHeight="1"/>
+    <row r="22" spans="2:21" ht="23" customHeight="1">
+      <c r="B22" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="66"/>
+    </row>
+    <row r="23" spans="2:21" ht="19" customHeight="1">
+      <c r="B23" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="15" customHeight="1">
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="2:21" ht="20" customHeight="1">
+      <c r="B25" s="6"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="O25" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="47"/>
+    </row>
+    <row r="26" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B26" s="6"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="O26" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="35"/>
+    </row>
+    <row r="27" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B27" s="6"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="38"/>
+    </row>
+    <row r="28" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="38"/>
+    </row>
+    <row r="29" spans="2:21" ht="17" customHeight="1">
+      <c r="B29" s="6"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="38"/>
+    </row>
+    <row r="30" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O30" s="36"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="38"/>
+    </row>
+    <row r="31" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O31" s="36"/>
+      <c r="P31" s="37"/>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="37"/>
+      <c r="S31" s="37"/>
+      <c r="T31" s="37"/>
+      <c r="U31" s="38"/>
+    </row>
+    <row r="32" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O32" s="36"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="37"/>
+      <c r="R32" s="37"/>
+      <c r="S32" s="37"/>
+      <c r="T32" s="37"/>
+      <c r="U32" s="38"/>
+    </row>
+    <row r="33" spans="15:21" ht="15.75" customHeight="1">
+      <c r="O33" s="36"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="37"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="38"/>
+    </row>
+    <row r="34" spans="15:21" ht="15.75" customHeight="1">
+      <c r="O34" s="36"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="38"/>
+    </row>
+    <row r="35" spans="15:21" ht="15.75" customHeight="1">
+      <c r="O35" s="36"/>
+      <c r="P35" s="37"/>
+      <c r="Q35" s="37"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="37"/>
+      <c r="T35" s="37"/>
+      <c r="U35" s="38"/>
+    </row>
+    <row r="36" spans="15:21" ht="15.75" customHeight="1">
+      <c r="O36" s="36"/>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="37"/>
+      <c r="S36" s="37"/>
+      <c r="T36" s="37"/>
+      <c r="U36" s="38"/>
+    </row>
+    <row r="37" spans="15:21" ht="15.75" customHeight="1">
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="40"/>
+      <c r="S37" s="40"/>
+      <c r="T37" s="40"/>
+      <c r="U37" s="41"/>
+    </row>
+    <row r="38" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="39" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="40" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="41" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="42" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="43" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="44" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="45" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="46" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="47" spans="15:21" ht="15.75" customHeight="1"/>
+    <row r="48" spans="15:21" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2327,32 +2457,30 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="P2:S2"/>
+  <mergeCells count="23">
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="O26:U37"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="B2:U2"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="M3:N4"/>
-    <mergeCell ref="B23:G34"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B8:F8"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="L13:M14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/app_lealtad/CheckListAppLealtad.xlsx
+++ b/app_lealtad/CheckListAppLealtad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/proyecto/app_lealtad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D44AB83-5133-484F-852D-BB697E93F166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79C2D21-9A9C-7740-8EA4-2C6803A520DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -545,9 +545,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -935,75 +932,75 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="30"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="27"/>
     </row>
     <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="22" t="s">
+      <c r="F3" s="20"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="22" t="s">
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="31" t="s">
+      <c r="L3" s="20"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="22" t="s">
+      <c r="Q3" s="20"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="23"/>
-      <c r="U3" s="24"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="21"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1031,8 +1028,8 @@
       <c r="M4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
       <c r="P4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1165,56 +1162,56 @@
     <row r="10" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="11" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="12" spans="2:21" ht="27" customHeight="1">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="14"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="11"/>
     </row>
     <row r="13" spans="2:21" ht="18" customHeight="1">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="17" t="s">
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="17" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="57" t="s">
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="58"/>
-      <c r="O13" s="48" t="s">
+      <c r="M13" s="55"/>
+      <c r="O13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="50"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="47"/>
     </row>
     <row r="14" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B14" s="16"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1239,18 +1236,18 @@
       <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="59"/>
-      <c r="M14" s="60"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="27"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="57"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="24"/>
     </row>
     <row r="15" spans="2:21" ht="15.75" customHeight="1">
       <c r="B15" s="1"/>
@@ -1262,77 +1259,77 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="20"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
-      <c r="U15" s="43"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="17"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="40"/>
     </row>
     <row r="16" spans="2:21" ht="15.75" customHeight="1">
       <c r="B16" s="2"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
-      <c r="U16" s="43"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="40"/>
     </row>
     <row r="17" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O17" s="12"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
     </row>
     <row r="18" spans="2:21" ht="27" customHeight="1">
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="H18" s="51" t="s">
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="H18" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="53"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="50"/>
     </row>
     <row r="19" spans="2:21" ht="19" customHeight="1">
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="56"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="53"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="53"/>
     </row>
     <row r="21" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="22" spans="2:21" ht="23" customHeight="1">
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="66"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="63"/>
     </row>
     <row r="23" spans="2:21" ht="19" customHeight="1">
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="64" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1356,141 +1353,141 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="O25" s="45" t="s">
+      <c r="O25" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="47"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="44"/>
     </row>
     <row r="26" spans="2:21" ht="15.75" customHeight="1">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="O26" s="33" t="s">
+      <c r="O26" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="32"/>
     </row>
     <row r="27" spans="2:21" ht="15.75" customHeight="1">
       <c r="B27" s="6"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="37"/>
-      <c r="S27" s="37"/>
-      <c r="T27" s="37"/>
-      <c r="U27" s="38"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="35"/>
     </row>
     <row r="28" spans="2:21" ht="15.75" customHeight="1">
       <c r="B28" s="6"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="O28" s="36"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="38"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="35"/>
     </row>
     <row r="29" spans="2:21" ht="17" customHeight="1">
       <c r="B29" s="6"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="38"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="35"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O30" s="36"/>
-      <c r="P30" s="37"/>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="37"/>
-      <c r="S30" s="37"/>
-      <c r="T30" s="37"/>
-      <c r="U30" s="38"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="35"/>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O31" s="36"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="38"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="35"/>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O32" s="36"/>
-      <c r="P32" s="37"/>
-      <c r="Q32" s="37"/>
-      <c r="R32" s="37"/>
-      <c r="S32" s="37"/>
-      <c r="T32" s="37"/>
-      <c r="U32" s="38"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="35"/>
     </row>
     <row r="33" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O33" s="36"/>
-      <c r="P33" s="37"/>
-      <c r="Q33" s="37"/>
-      <c r="R33" s="37"/>
-      <c r="S33" s="37"/>
-      <c r="T33" s="37"/>
-      <c r="U33" s="38"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="35"/>
     </row>
     <row r="34" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O34" s="36"/>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="37"/>
-      <c r="R34" s="37"/>
-      <c r="S34" s="37"/>
-      <c r="T34" s="37"/>
-      <c r="U34" s="38"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="35"/>
     </row>
     <row r="35" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O35" s="36"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="37"/>
-      <c r="S35" s="37"/>
-      <c r="T35" s="37"/>
-      <c r="U35" s="38"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="34"/>
+      <c r="U35" s="35"/>
     </row>
     <row r="36" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O36" s="36"/>
-      <c r="P36" s="37"/>
-      <c r="Q36" s="37"/>
-      <c r="R36" s="37"/>
-      <c r="S36" s="37"/>
-      <c r="T36" s="37"/>
-      <c r="U36" s="38"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="35"/>
     </row>
     <row r="37" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="41"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="37"/>
+      <c r="S37" s="37"/>
+      <c r="T37" s="37"/>
+      <c r="U37" s="38"/>
     </row>
     <row r="38" spans="15:21" ht="15.75" customHeight="1"/>
     <row r="39" spans="15:21" ht="15.75" customHeight="1"/>
@@ -2457,10 +2454,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B12:L12"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="O26:U37"/>
     <mergeCell ref="O15:U15"/>
     <mergeCell ref="O16:U16"/>

--- a/app_lealtad/CheckListAppLealtad.xlsx
+++ b/app_lealtad/CheckListAppLealtad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/proyecto/app_lealtad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79C2D21-9A9C-7740-8EA4-2C6803A520DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39060204-9445-E044-889A-1B4EF7A8E3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
     <t>System Status</t>
   </si>
@@ -109,12 +109,15 @@
   <si>
     <t>ERROR EN LOS LOGS EN "database-1ceca-resp-instance-1-reader"</t>
   </si>
+  <si>
+    <t>Status</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -179,6 +182,12 @@
       <color theme="0"/>
       <name val="Aptos Narrow (Cuerpo)"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -236,7 +245,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -529,11 +538,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -553,33 +608,87 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -590,55 +699,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -649,48 +719,45 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,75 +999,75 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="27"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="43"/>
     </row>
     <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="19" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="19" t="s">
+      <c r="I3" s="47"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="28" t="s">
+      <c r="L3" s="47"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="28" t="s">
+      <c r="O3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="19" t="s">
+      <c r="Q3" s="47"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="20"/>
-      <c r="U3" s="21"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="48"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1028,8 +1095,8 @@
       <c r="M4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1162,123 +1229,99 @@
     <row r="10" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="11" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="12" spans="2:21" ht="27" customHeight="1">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="11"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
+      <c r="N12" s="61"/>
     </row>
     <row r="13" spans="2:21" ht="18" customHeight="1">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="14" t="s">
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="14" t="s">
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="54" t="s">
+      <c r="K13" s="56"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="55"/>
-      <c r="O13" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="47"/>
+      <c r="N13" s="59"/>
     </row>
     <row r="14" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B14" s="13"/>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="63"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="56"/>
-      <c r="M14" s="57"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="24"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="60"/>
     </row>
     <row r="15" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="65"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="17"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="40"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="11"/>
     </row>
     <row r="16" spans="2:21" ht="15.75" customHeight="1">
       <c r="B16" s="2"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="39"/>
-      <c r="U16" s="40"/>
     </row>
     <row r="17" spans="2:21" ht="15.75" customHeight="1">
       <c r="O17" s="9"/>
@@ -1290,46 +1333,79 @@
       <c r="U17" s="10"/>
     </row>
     <row r="18" spans="2:21" ht="27" customHeight="1">
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="H18" s="48" t="s">
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="H18" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="50"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="53"/>
+      <c r="O18" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="40"/>
     </row>
     <row r="19" spans="2:21" ht="19" customHeight="1">
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="53"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="53"/>
-    </row>
-    <row r="21" spans="2:21" ht="15.75" customHeight="1"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="22"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="22"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="50"/>
+    </row>
+    <row r="20" spans="2:21" ht="15" customHeight="1">
+      <c r="O20" s="32"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="34"/>
+    </row>
+    <row r="21" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O21" s="32"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="34"/>
+    </row>
     <row r="22" spans="2:21" ht="23" customHeight="1">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="2:21" ht="19" customHeight="1">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1353,141 +1429,141 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="O25" s="42" t="s">
+      <c r="O25" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="44"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="37"/>
     </row>
     <row r="26" spans="2:21" ht="15.75" customHeight="1">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="O26" s="30" t="s">
+      <c r="O26" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="32"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="25"/>
     </row>
     <row r="27" spans="2:21" ht="15.75" customHeight="1">
       <c r="B27" s="6"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="28"/>
     </row>
     <row r="28" spans="2:21" ht="15.75" customHeight="1">
       <c r="B28" s="6"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="28"/>
     </row>
     <row r="29" spans="2:21" ht="17" customHeight="1">
       <c r="B29" s="6"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="28"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O30" s="33"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="28"/>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O31" s="33"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="35"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="28"/>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O32" s="33"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="35"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="28"/>
     </row>
     <row r="33" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O33" s="33"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="35"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="28"/>
     </row>
     <row r="34" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O34" s="33"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="35"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="28"/>
     </row>
     <row r="35" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O35" s="33"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="35"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="28"/>
     </row>
     <row r="36" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O36" s="33"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="35"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="28"/>
     </row>
     <row r="37" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O37" s="36"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="37"/>
-      <c r="R37" s="37"/>
-      <c r="S37" s="37"/>
-      <c r="T37" s="37"/>
-      <c r="U37" s="38"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="31"/>
     </row>
     <row r="38" spans="15:21" ht="15.75" customHeight="1"/>
     <row r="39" spans="15:21" ht="15.75" customHeight="1"/>
@@ -2454,16 +2530,10 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="O26:U37"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="O13:U13"/>
+  <mergeCells count="28">
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="M13:N14"/>
+    <mergeCell ref="B12:N12"/>
     <mergeCell ref="B2:U2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -2475,10 +2545,20 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="P3:R3"/>
-    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="O26:U37"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="O18:U18"/>
+    <mergeCell ref="O19:U19"/>
     <mergeCell ref="H18:M18"/>
     <mergeCell ref="H19:M19"/>
-    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:L13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/app_lealtad/CheckListAppLealtad.xlsx
+++ b/app_lealtad/CheckListAppLealtad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/proyecto/app_lealtad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39060204-9445-E044-889A-1B4EF7A8E3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A79EE6E-B36A-4B41-9B1D-468F75E26E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>System Status</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>Disponibilidad de la URL / Página web</t>
-  </si>
-  <si>
-    <t>Free Storages Space Last Hour</t>
   </si>
   <si>
     <t>La revisión realizada se basa en los siguientes criterios:
@@ -245,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -541,19 +538,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -588,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -600,9 +584,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -613,9 +594,47 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -690,20 +709,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -719,11 +724,8 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -731,33 +733,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,75 +977,75 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="43"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="26"/>
     </row>
     <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="46" t="s">
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="46" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="47"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="44" t="s">
+      <c r="L3" s="30"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="44" t="s">
+      <c r="O3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="46" t="s">
+      <c r="P3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="46" t="s">
+      <c r="Q3" s="30"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="47"/>
-      <c r="U3" s="48"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="31"/>
     </row>
     <row r="4" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1095,8 +1073,8 @@
       <c r="M4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
       <c r="P4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1229,52 +1207,60 @@
     <row r="10" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="11" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="12" spans="2:21" ht="27" customHeight="1">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="O12" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="57"/>
     </row>
     <row r="13" spans="2:21" ht="18" customHeight="1">
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="67" t="s">
+      <c r="C13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="56" t="s">
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="56"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="54" t="s">
+      <c r="H13" s="64"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="N13" s="59"/>
+      <c r="K13" s="20"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="59"/>
     </row>
     <row r="14" spans="2:21" ht="19.5" customHeight="1">
-      <c r="B14" s="63"/>
-      <c r="C14" s="66"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="4" t="s">
         <v>8</v>
       </c>
@@ -1284,7 +1270,7 @@
       <c r="F14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="15" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
@@ -1293,119 +1279,88 @@
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" s="55"/>
-      <c r="N14" s="60"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="51"/>
     </row>
     <row r="15" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B15" s="8"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="65"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="16"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="10"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="50"/>
+      <c r="T15" s="50"/>
+      <c r="U15" s="51"/>
     </row>
     <row r="16" spans="2:21" ht="15.75" customHeight="1">
       <c r="B16" s="2"/>
     </row>
     <row r="17" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O17" s="9"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
     </row>
     <row r="18" spans="2:21" ht="27" customHeight="1">
-      <c r="B18" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="H18" s="51" t="s">
+      <c r="B18" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="H18" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="53"/>
-      <c r="O18" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="39"/>
-      <c r="U18" s="40"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
     </row>
     <row r="19" spans="2:21" ht="19" customHeight="1">
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="22"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="22"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="50"/>
-    </row>
-    <row r="20" spans="2:21" ht="15" customHeight="1">
-      <c r="O20" s="32"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="34"/>
-    </row>
-    <row r="21" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O21" s="32"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="34"/>
-    </row>
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="39"/>
+    </row>
+    <row r="21" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="22" spans="2:21" ht="23" customHeight="1">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23" spans="2:21" ht="19" customHeight="1">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1429,141 +1384,141 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="O25" s="35" t="s">
+      <c r="O25" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="36"/>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="37"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="53"/>
+      <c r="U25" s="54"/>
     </row>
     <row r="26" spans="2:21" ht="15.75" customHeight="1">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="O26" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="25"/>
+      <c r="O26" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="42"/>
     </row>
     <row r="27" spans="2:21" ht="15.75" customHeight="1">
       <c r="B27" s="6"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="28"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="45"/>
     </row>
     <row r="28" spans="2:21" ht="15.75" customHeight="1">
       <c r="B28" s="6"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="28"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="45"/>
     </row>
     <row r="29" spans="2:21" ht="17" customHeight="1">
       <c r="B29" s="6"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="28"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="45"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O30" s="26"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="28"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="45"/>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O31" s="26"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="28"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="45"/>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O32" s="26"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="28"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="45"/>
     </row>
     <row r="33" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O33" s="26"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="28"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="45"/>
     </row>
     <row r="34" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O34" s="26"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="28"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="45"/>
     </row>
     <row r="35" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O35" s="26"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="28"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="45"/>
     </row>
     <row r="36" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O36" s="26"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="28"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="44"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="45"/>
     </row>
     <row r="37" spans="15:21" ht="15.75" customHeight="1">
-      <c r="O37" s="29"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="31"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="47"/>
+      <c r="Q37" s="47"/>
+      <c r="R37" s="47"/>
+      <c r="S37" s="47"/>
+      <c r="T37" s="47"/>
+      <c r="U37" s="48"/>
     </row>
     <row r="38" spans="15:21" ht="15.75" customHeight="1"/>
     <row r="39" spans="15:21" ht="15.75" customHeight="1"/>
@@ -2530,10 +2485,21 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="O26:U37"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="H19:M19"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="M13:N14"/>
-    <mergeCell ref="B12:N12"/>
+    <mergeCell ref="J13:K14"/>
     <mergeCell ref="B2:U2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -2545,20 +2511,8 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="P3:R3"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="O26:U37"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="O18:U18"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="H19:M19"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:L13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
